--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488008_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488008_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. RAMOS ANGULO</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6119</v>
+        <v>6.2847</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3125</v>
+        <v>5.5803</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2994</v>
+        <v>0.7044</v>
       </c>
       <c r="G2" t="n">
-        <v>4.7655</v>
+        <v>4.7393</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.9922</v>
+        <v>0.911</v>
       </c>
       <c r="I2" t="n">
-        <v>6.7576</v>
+        <v>3.8283</v>
       </c>
       <c r="J2" t="n">
-        <v>5.0061</v>
+        <v>5.7175</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.1968</v>
+        <v>1.7762</v>
       </c>
       <c r="L2" t="n">
-        <v>6.2029</v>
+        <v>3.9413</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2406</v>
+        <v>-0.9782</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7953</v>
+        <v>-0.8652</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5547</v>
+        <v>-0.113</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3964</v>
+        <v>1.784</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.1805</v>
+        <v>-0.9911</v>
       </c>
       <c r="R2" t="n">
-        <v>1.784</v>
+        <v>2.7751</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2429</v>
+        <v>0.1487</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4868</v>
+        <v>-0.3532</v>
       </c>
       <c r="U2" t="n">
-        <v>0.756</v>
+        <v>0.5019</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>-0.3873</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.5944</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>J. RAMOS ANGULO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9719</v>
+        <v>5.5161</v>
       </c>
       <c r="E3" t="n">
-        <v>5.071</v>
+        <v>3.4975</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9009</v>
+        <v>2.0186</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7393</v>
+        <v>4.7655</v>
       </c>
       <c r="H3" t="n">
-        <v>0.911</v>
+        <v>-1.9922</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8283</v>
+        <v>6.7576</v>
       </c>
       <c r="J3" t="n">
-        <v>5.7175</v>
+        <v>5.0061</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7762</v>
+        <v>-1.1968</v>
       </c>
       <c r="L3" t="n">
-        <v>3.9413</v>
+        <v>6.2029</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9782</v>
+        <v>-0.2406</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8652</v>
+        <v>-0.7953</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.113</v>
+        <v>0.5547</v>
       </c>
       <c r="P3" t="n">
+        <v>-0.3964</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-2.1805</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.784</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-0.9911</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.7751</v>
-      </c>
       <c r="S3" t="n">
-        <v>-0.1641</v>
+        <v>1.1471</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8625</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6984</v>
+        <v>0.4752</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3873</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.5944</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. COBOS ORTEGA</t>
+          <t>P. CARRASCO LOBO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0483</v>
+        <v>3.1373</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7818</v>
+        <v>0.9475</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7335</v>
+        <v>2.1898</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7899</v>
+        <v>1.82</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1659</v>
+        <v>1.3667</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9558</v>
+        <v>0.4534</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7603</v>
+        <v>2.2799</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8273</v>
+        <v>2.2397</v>
       </c>
       <c r="L4" t="n">
-        <v>2.933</v>
+        <v>0.0402</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9704</v>
+        <v>-0.4599</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9932</v>
+        <v>-0.8731</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0228</v>
+        <v>0.4132</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1982</v>
+        <v>0.9911</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1893</v>
+        <v>-0.9911</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3876</v>
+        <v>1.9822</v>
       </c>
       <c r="S4" t="n">
-        <v>0.181</v>
+        <v>-0.3478</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0038</v>
+        <v>-0.3413</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1772</v>
+        <v>-0.0065</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1207</v>
+        <v>0.674</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.3278</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. IBÁÑEZ FIDALGO</t>
+          <t>C. COBOS ORTEGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7133</v>
+        <v>3.1326</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7133</v>
+        <v>3.7818</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0.6492</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7133</v>
+        <v>2.7899</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3027</v>
+        <v>-0.1659</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4107</v>
+        <v>2.9558</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7133</v>
+        <v>3.7603</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3027</v>
+        <v>0.8273</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4107</v>
+        <v>2.933</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.9704</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.9932</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.0228</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.2652</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.0038</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.2614</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.1207</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.3278</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. CARRASCO LOBO</t>
+          <t>P. IBÁÑEZ FIDALGO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6456</v>
+        <v>2.7133</v>
       </c>
       <c r="E6" t="n">
-        <v>0.54</v>
+        <v>2.7133</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1056</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.82</v>
+        <v>2.7133</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3667</v>
+        <v>0.3027</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4534</v>
+        <v>2.4107</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2799</v>
+        <v>2.7133</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2397</v>
+        <v>0.3027</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0402</v>
+        <v>2.4107</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8731</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4132</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9822</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8395</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7488</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0907</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2771</v>
+        <v>2.1015</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7156</v>
+        <v>1.5119</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5615</v>
+        <v>0.5896</v>
       </c>
       <c r="G7" t="n">
         <v>0.2602</v>
@@ -1000,13 +1000,13 @@
         <v>1.5858</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2081</v>
+        <v>1.0324</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8701</v>
+        <v>0.6664</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3379</v>
+        <v>0.366</v>
       </c>
       <c r="V7" t="n">
         <v>0.4124</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9977</v>
+        <v>1.6745</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2</v>
+        <v>0.7925</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7977</v>
+        <v>0.8819</v>
       </c>
       <c r="G8" t="n">
         <v>1.189</v>
@@ -1078,13 +1078,13 @@
         <v>0.1982</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6105</v>
+        <v>0.2873</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5543</v>
+        <v>0.1469</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0562</v>
+        <v>0.1404</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3051</v>
+        <v>0.7501</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0751</v>
+        <v>0.4638</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2301</v>
+        <v>0.2862</v>
       </c>
       <c r="G9" t="n">
         <v>0.3632</v>
@@ -1156,13 +1156,13 @@
         <v>0.5947</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8121</v>
+        <v>0.257</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9839</v>
+        <v>0.3727</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1718</v>
+        <v>-0.1157</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2666</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5289</v>
+        <v>0.4166</v>
       </c>
       <c r="E10" t="n">
         <v>-0.0422</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5712</v>
+        <v>0.4588</v>
       </c>
       <c r="G10" t="n">
         <v>0.156</v>
@@ -1234,13 +1234,13 @@
         <v>0.1982</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1747</v>
+        <v>0.0624</v>
       </c>
       <c r="T10" t="n">
         <v>-0.0624</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2371</v>
+        <v>0.1248</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1408</v>
+        <v>0.0348</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0741</v>
+        <v>0.2778</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2149</v>
+        <v>-0.243</v>
       </c>
       <c r="G12" t="n">
         <v>1.1226</v>
@@ -1390,13 +1390,13 @@
         <v>1.9822</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4886</v>
+        <v>-0.3129</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.7212</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4363</v>
+        <v>0.4083</v>
       </c>
       <c r="V12" t="n">
         <v>0.2163</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.9151</v>
+        <v>-0.3568</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.7231</v>
+        <v>-0.4175</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.192</v>
+        <v>0.0607</v>
       </c>
       <c r="G13" t="n">
         <v>-0.1137</v>
@@ -1468,13 +1468,13 @@
         <v>2.3787</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2484</v>
+        <v>-0.6901</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.6304</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3124</v>
+        <v>-0.0597</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9405</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.9785</v>
+        <v>-0.8414</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.2699</v>
+        <v>-0.9643</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2914</v>
+        <v>0.1229</v>
       </c>
       <c r="G14" t="n">
         <v>-1.4628</v>
@@ -1546,13 +1546,13 @@
         <v>1.5858</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.4561</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.6304</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3427</v>
+        <v>0.1743</v>
       </c>
       <c r="V14" t="n">
         <v>0.4828</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.2248</v>
+        <v>-1.7226</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.4853</v>
+        <v>-1.1797</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7395</v>
+        <v>-0.543</v>
       </c>
       <c r="G15" t="n">
         <v>-1.574</v>
@@ -1624,13 +1624,13 @@
         <v>0.3964</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8491</v>
+        <v>-0.3469</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4368</v>
+        <v>-0.1312</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4123</v>
+        <v>-0.2157</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>23.1433</v>
+        <v>23.1434</v>
       </c>
       <c r="E16" t="n">
-        <v>17.2656</v>
+        <v>17.2654</v>
       </c>
       <c r="F16" t="n">
-        <v>5.8779</v>
+        <v>5.877699999999999</v>
       </c>
       <c r="G16" t="n">
         <v>17.07119999999999</v>
@@ -1693,7 +1693,7 @@
         <v>2.18</v>
       </c>
       <c r="P16" t="n">
-        <v>4.955499999999999</v>
+        <v>4.955500000000001</v>
       </c>
       <c r="Q16" t="n">
         <v>-11.8932</v>
@@ -1702,13 +1702,13 @@
         <v>16.8489</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0464</v>
+        <v>1.0463</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0085</v>
+        <v>-1.0084</v>
       </c>
       <c r="U16" t="n">
-        <v>2.0546</v>
+        <v>2.0547</v>
       </c>
       <c r="V16" t="n">
         <v>0.07040000000000002</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6736</v>
+        <v>2.5672</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4894</v>
+        <v>3.3875</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8158</v>
+        <v>-0.8203</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0319</v>
@@ -1780,13 +1780,13 @@
         <v>2.1805</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0019</v>
+        <v>-0.1083</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3816</v>
+        <v>-0.4835</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3797</v>
+        <v>0.3752</v>
       </c>
       <c r="V17" t="n">
         <v>4.4914</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>W. HASSAN</t>
+          <t>A. GUZMAN SALINAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0092</v>
+        <v>0.0551</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3625</v>
+        <v>1.8681</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3533</v>
+        <v>-1.813</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.384</v>
+        <v>-0.9415</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7559</v>
+        <v>0.063</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.6281</v>
+        <v>-1.0044</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3446</v>
+        <v>1.1041</v>
       </c>
       <c r="K18" t="n">
-        <v>0.377</v>
+        <v>1.0561</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0324</v>
+        <v>0.048</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.7286</v>
+        <v>-2.0456</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1329</v>
+        <v>-0.9932</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5957</v>
+        <v>-1.0524</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5858</v>
+        <v>1.3876</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5858</v>
+        <v>1.3876</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4483</v>
+        <v>-0.391</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4847</v>
+        <v>-0.4432</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0364</v>
+        <v>0.0521</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3591</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5331</v>
+        <v>1.2071</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.174</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GUZMAN SALINAS</t>
+          <t>W. HASSAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0022</v>
+        <v>-0.2684</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5624</v>
+        <v>1.0569</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5603</v>
+        <v>-1.3252</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9415</v>
+        <v>-2.384</v>
       </c>
       <c r="H19" t="n">
-        <v>0.063</v>
+        <v>-0.7559</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0044</v>
+        <v>-1.6281</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1041</v>
+        <v>0.3446</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0561</v>
+        <v>0.377</v>
       </c>
       <c r="L19" t="n">
-        <v>0.048</v>
+        <v>-0.0324</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0456</v>
+        <v>-2.7286</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9932</v>
+        <v>-1.1329</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0524</v>
+        <v>-1.5957</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3876</v>
+        <v>1.5858</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3876</v>
+        <v>1.5858</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4439</v>
+        <v>0.1707</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7488</v>
+        <v>0.1791</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3049</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3591</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2071</v>
+        <v>0.5331</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2071</v>
+        <v>-0.174</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5405</v>
+        <v>-0.34</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.606</v>
+        <v>-1.0966</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0655</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7904</v>
@@ -2014,13 +2014,13 @@
         <v>1.1893</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0518</v>
+        <v>0.1487</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6864</v>
+        <v>-0.177</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.3257</v>
       </c>
       <c r="V20" t="n">
         <v>1.1035</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5798</v>
+        <v>-0.8012</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9709</v>
+        <v>-1.2765</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3911</v>
+        <v>0.4753</v>
       </c>
       <c r="G21" t="n">
         <v>-1.8019</v>
@@ -2092,13 +2092,13 @@
         <v>0.3964</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1516</v>
+        <v>-0.0697</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3671</v>
+        <v>0.0615</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2155</v>
+        <v>-0.1313</v>
       </c>
       <c r="V21" t="n">
         <v>0.674</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5734</v>
+        <v>-1.5277</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7749</v>
+        <v>-1.673</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2015</v>
+        <v>0.1453</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8568</v>
@@ -2170,13 +2170,13 @@
         <v>0.3964</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1219</v>
+        <v>-0.0762</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1248</v>
+        <v>-0.0229</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0029</v>
+        <v>-0.0533</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9269</v>
+        <v>-1.7454</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4338</v>
+        <v>-1.3319</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4931</v>
+        <v>-0.4135</v>
       </c>
       <c r="G23" t="n">
         <v>0.2022</v>
@@ -2248,13 +2248,13 @@
         <v>0.5947</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2064</v>
+        <v>-0.0248</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5616</v>
+        <v>-0.4597</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3552</v>
+        <v>0.4349</v>
       </c>
       <c r="V23" t="n">
         <v>-0.337</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7682</v>
+        <v>-3.3901</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9224</v>
+        <v>-0.8206</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8457</v>
+        <v>-2.5695</v>
       </c>
       <c r="G24" t="n">
         <v>-0.5094</v>
@@ -2326,13 +2326,13 @@
         <v>0.7929</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.49</v>
+        <v>-0.112</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.624</v>
+        <v>-0.5221</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1339</v>
+        <v>0.4102</v>
       </c>
       <c r="V24" t="n">
         <v>-1.3811</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.1443</v>
+        <v>-3.5449</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.0625</v>
+        <v>-1.655</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0818</v>
+        <v>-1.8898</v>
       </c>
       <c r="G25" t="n">
         <v>-1.1062</v>
@@ -2404,13 +2404,13 @@
         <v>0.7929</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4435</v>
+        <v>0.156</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5616</v>
+        <v>-0.1541</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1181</v>
+        <v>0.3101</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2071</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.2251</v>
+        <v>-5.9632</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.6571</v>
+        <v>-2.0646</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.568</v>
+        <v>-3.8986</v>
       </c>
       <c r="G26" t="n">
         <v>-4.6771</v>
@@ -2482,13 +2482,13 @@
         <v>1.1893</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4334</v>
+        <v>-0.1716</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2975</v>
+        <v>-0.11</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.7309</v>
+        <v>-0.0616</v>
       </c>
       <c r="V26" t="n">
         <v>-1.1146</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-7.0701</v>
+        <v>-7.5056</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.8645</v>
+        <v>-2.272</v>
       </c>
       <c r="F27" t="n">
-        <v>-5.2056</v>
+        <v>-5.2337</v>
       </c>
       <c r="G27" t="n">
         <v>-3.1741</v>
@@ -2560,13 +2560,13 @@
         <v>1.3876</v>
       </c>
       <c r="S27" t="n">
-        <v>0.5466</v>
+        <v>0.1111</v>
       </c>
       <c r="T27" t="n">
-        <v>0.4847</v>
+        <v>0.0772</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0619</v>
+        <v>0.0339</v>
       </c>
       <c r="V27" t="n">
         <v>-2.6586</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-23.1433</v>
+        <v>-22.4642</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.877800000000001</v>
+        <v>-5.877699999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>-17.2655</v>
+        <v>-16.5864</v>
       </c>
       <c r="G28" t="n">
         <v>-17.0711</v>
@@ -2638,19 +2638,19 @@
         <v>11.8934</v>
       </c>
       <c r="S28" t="n">
-        <v>-1.0463</v>
+        <v>-0.3671</v>
       </c>
       <c r="T28" t="n">
-        <v>-2.0548</v>
+        <v>-2.0547</v>
       </c>
       <c r="U28" t="n">
-        <v>1.0084</v>
+        <v>1.6875</v>
       </c>
       <c r="V28" t="n">
-        <v>-0.07040000000000113</v>
+        <v>-0.07039999999999935</v>
       </c>
       <c r="W28" t="n">
-        <v>6.5536</v>
+        <v>6.553599999999999</v>
       </c>
       <c r="X28" t="n">
         <v>-6.624000000000001</v>
